--- a/artfynd/A 30458-2026 artfynd.xlsx
+++ b/artfynd/A 30458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,127 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135315645</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96783</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Måsebo Hyttekärr, Måsebo Hyttekärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587683</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6417155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många kuddar inom 10 m2</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30458-2026 artfynd.xlsx
+++ b/artfynd/A 30458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,132 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132770159</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135315645</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96859</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Måsebo Hyttekärr, Måsebo Hyttekärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587683</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6417155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många kuddar inom 10 m2</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135315645</t>
         </is>
       </c>
     </row>
@@ -1052,6 +1178,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30458-2026 artfynd.xlsx
+++ b/artfynd/A 30458-2026 artfynd.xlsx
@@ -1052,7 +1052,7 @@
         <v>135315645</v>
       </c>
       <c r="B5" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
